--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T12:12:39+00:00</t>
+    <t>2024-11-05T09:00:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T09:00:17+00:00</t>
+    <t>2024-11-05T09:16:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T09:16:22+00:00</t>
+    <t>2024-11-05T10:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T10:26:22+00:00</t>
+    <t>2024-11-06T09:40:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T09:40:37+00:00</t>
+    <t>2024-11-07T06:21:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T06:21:30+00:00</t>
+    <t>2024-11-07T13:12:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T13:12:32+00:00</t>
+    <t>2024-11-07T14:31:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T14:31:26+00:00</t>
+    <t>2024-11-08T06:37:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDAccount.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2618" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2584" uniqueCount="408">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T06:16:09+00:00</t>
+    <t>2024-11-12T07:45:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -476,24 +476,6 @@
   </si>
   <si>
     <t>MOPED Extension für die Anzahl der Beurlaubungen</t>
-  </si>
-  <si>
-    <t>Account.extension:vdasid</t>
-  </si>
-  <si>
-    <t>vdasid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-vdasid}
-</t>
-  </si>
-  <si>
-    <t>VDAS-ID - VersichertenDatenAbfrageService</t>
-  </si>
-  <si>
-    <t>Es handelt sich um eine ID, welche bei der VDAS-Abfrage durch die Krankenanstalt vom e-card System vergeben wird und von der Krankenanstalt in der Aufnahme-/Ereignisanzeige mitgeliefert werden kann. Dadurch kann das Abfrageergebnis eindeutig nachvollzogen werden.
-Das Ergebnis der VDAS-Abfrage ist im ambulanten Bereich für den Krankenversicherungsträger verbindlich. Eine Ablehnung aus versicherungsrechtlichen Gründen ist nicht möglich, sofern die Er- eignisanzeige jenem Träger aus der VDAS-Abfrage (inkl. VDAS-ID) übermittelt wurde.
-Um eine zwischenstaatliche Verrechnung zu ermöglichen ist bei zwischenstaatlichen Fällen eine Ablehnung zulässig.</t>
   </si>
   <si>
     <t>Account.extension:workflowStatus</t>
@@ -1616,7 +1598,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL77"/>
+  <dimension ref="A1:AL76"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="46.40234375" customWidth="true" bestFit="true"/>
@@ -2861,7 +2843,7 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>84</v>
@@ -2969,7 +2951,7 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>84</v>
@@ -3499,41 +3481,43 @@
         <v>178</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="C18" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="D18" t="s" s="2">
-        <v>19</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
+      <c r="O18" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>19</v>
       </c>
@@ -3581,7 +3565,7 @@
         <v>19</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>136</v>
+        <v>184</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>75</v>
@@ -3599,19 +3583,19 @@
         <v>19</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>19</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>184</v>
+        <v>19</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3624,26 +3608,22 @@
         <v>19</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>131</v>
+        <v>186</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="O19" t="s" s="2">
         <v>188</v>
       </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>19</v>
       </c>
@@ -3691,7 +3671,7 @@
         <v>19</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>75</v>
@@ -3703,21 +3683,21 @@
         <v>19</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>19</v>
+        <v>189</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>129</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3725,22 +3705,22 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>191</v>
+        <v>104</v>
       </c>
       <c r="L20" t="s" s="2">
         <v>192</v>
@@ -3748,7 +3728,9 @@
       <c r="M20" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="N20" s="2"/>
+      <c r="N20" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>19</v>
@@ -3773,13 +3755,13 @@
         <v>19</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>19</v>
+        <v>108</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>19</v>
+        <v>195</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>19</v>
+        <v>196</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>19</v>
@@ -3797,13 +3779,13 @@
         <v>19</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>19</v>
@@ -3812,18 +3794,18 @@
         <v>96</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3831,7 +3813,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>84</v>
@@ -3840,23 +3822,21 @@
         <v>19</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>104</v>
+        <v>200</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>199</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>19</v>
@@ -3881,13 +3861,13 @@
         <v>19</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>108</v>
+        <v>203</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>19</v>
@@ -3905,10 +3885,10 @@
         <v>19</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>84</v>
@@ -3920,18 +3900,18 @@
         <v>96</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>203</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3954,13 +3934,13 @@
         <v>85</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3987,7 +3967,7 @@
         <v>19</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="Y22" t="s" s="2">
         <v>209</v>
@@ -4011,7 +3991,7 @@
         <v>19</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>75</v>
@@ -4026,22 +4006,22 @@
         <v>96</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>19</v>
+        <v>211</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>19</v>
+        <v>212</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>19</v>
+        <v>214</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4060,13 +4040,13 @@
         <v>85</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4093,13 +4073,13 @@
         <v>19</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>208</v>
+        <v>19</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>214</v>
+        <v>19</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>215</v>
+        <v>19</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>19</v>
@@ -4117,7 +4097,7 @@
         <v>19</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>75</v>
@@ -4132,29 +4112,29 @@
         <v>96</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>19</v>
@@ -4166,15 +4146,17 @@
         <v>85</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>224</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>19</v>
@@ -4223,13 +4205,13 @@
         <v>19</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>19</v>
@@ -4238,29 +4220,29 @@
         <v>96</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>226</v>
+        <v>19</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>19</v>
@@ -4272,16 +4254,16 @@
         <v>85</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4331,13 +4313,13 @@
         <v>19</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>19</v>
@@ -4346,18 +4328,18 @@
         <v>96</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4368,7 +4350,7 @@
         <v>75</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>19</v>
@@ -4380,16 +4362,16 @@
         <v>85</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4439,13 +4421,13 @@
         <v>19</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>19</v>
@@ -4454,18 +4436,18 @@
         <v>96</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>238</v>
+        <v>19</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4476,7 +4458,7 @@
         <v>75</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>19</v>
@@ -4485,10 +4467,10 @@
         <v>19</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>241</v>
+        <v>215</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>242</v>
@@ -4496,9 +4478,7 @@
       <c r="M27" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="N27" t="s" s="2">
-        <v>244</v>
-      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>19</v>
@@ -4547,44 +4527,44 @@
         <v>19</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>19</v>
+        <v>245</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>96</v>
+        <v>19</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>19</v>
+        <v>179</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>19</v>
@@ -4596,15 +4576,17 @@
         <v>19</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>220</v>
+        <v>131</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>19</v>
@@ -4653,37 +4635,37 @@
         <v>19</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>250</v>
+        <v>19</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>184</v>
+        <v>252</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4696,10 +4678,10 @@
         <v>19</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
         <v>131</v>
@@ -4711,9 +4693,11 @@
         <v>254</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>19</v>
       </c>
@@ -4779,7 +4763,7 @@
         <v>19</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>251</v>
+        <v>129</v>
       </c>
     </row>
     <row r="30">
@@ -4791,26 +4775,26 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>257</v>
+        <v>19</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="J30" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>131</v>
+        <v>257</v>
       </c>
       <c r="L30" t="s" s="2">
         <v>258</v>
@@ -4818,12 +4802,8 @@
       <c r="M30" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="N30" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>188</v>
-      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>19</v>
       </c>
@@ -4871,25 +4851,25 @@
         <v>19</v>
       </c>
       <c r="AF30" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="AG30" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AJ30" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AK30" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>129</v>
       </c>
     </row>
     <row r="31">
@@ -4901,11 +4881,11 @@
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>19</v>
+        <v>262</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>84</v>
@@ -4920,15 +4900,17 @@
         <v>85</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>19</v>
@@ -4980,7 +4962,7 @@
         <v>261</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>84</v>
@@ -4995,19 +4977,19 @@
         <v>19</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>267</v>
+        <v>19</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5026,17 +5008,15 @@
         <v>85</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N32" t="s" s="2">
         <v>271</v>
       </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>19</v>
@@ -5085,7 +5065,7 @@
         <v>19</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>75</v>
@@ -5228,7 +5208,7 @@
         <v>75</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>19</v>
@@ -5237,16 +5217,16 @@
         <v>19</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5303,7 +5283,7 @@
         <v>75</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>19</v>
@@ -5315,15 +5295,15 @@
         <v>19</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5334,7 +5314,7 @@
         <v>75</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>19</v>
@@ -5346,13 +5326,13 @@
         <v>19</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>241</v>
+        <v>215</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>284</v>
+        <v>242</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>285</v>
+        <v>243</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5403,44 +5383,44 @@
         <v>19</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>283</v>
+        <v>244</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>19</v>
+        <v>245</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>96</v>
+        <v>19</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>286</v>
+        <v>246</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>19</v>
+        <v>179</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>19</v>
@@ -5452,15 +5432,17 @@
         <v>19</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>220</v>
+        <v>131</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>19</v>
@@ -5509,37 +5491,37 @@
         <v>19</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>250</v>
+        <v>19</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>184</v>
+        <v>252</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5552,10 +5534,10 @@
         <v>19</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="K37" t="s" s="2">
         <v>131</v>
@@ -5567,9 +5549,11 @@
         <v>254</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>19</v>
       </c>
@@ -5635,51 +5619,47 @@
         <v>19</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>251</v>
+        <v>129</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>257</v>
+        <v>19</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>131</v>
+        <v>286</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>258</v>
+        <v>287</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>19</v>
       </c>
@@ -5727,25 +5707,25 @@
         <v>19</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>260</v>
+        <v>285</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>129</v>
+        <v>289</v>
       </c>
     </row>
     <row r="39">
@@ -5761,7 +5741,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>84</v>
@@ -5836,7 +5816,7 @@
         <v>290</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>84</v>
@@ -5882,13 +5862,13 @@
         <v>19</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5957,15 +5937,15 @@
         <v>19</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5976,7 +5956,7 @@
         <v>75</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>19</v>
@@ -5985,16 +5965,16 @@
         <v>19</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6045,33 +6025,33 @@
         <v>19</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>96</v>
+        <v>302</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>303</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6082,7 +6062,7 @@
         <v>75</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>19</v>
@@ -6091,16 +6071,16 @@
         <v>19</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>241</v>
+        <v>215</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>305</v>
+        <v>242</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>306</v>
+        <v>243</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6151,44 +6131,44 @@
         <v>19</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>304</v>
+        <v>244</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>19</v>
+        <v>245</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>307</v>
+        <v>19</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>19</v>
+        <v>246</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>19</v>
+        <v>179</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>19</v>
@@ -6200,15 +6180,17 @@
         <v>19</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>220</v>
+        <v>131</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>19</v>
@@ -6257,37 +6239,37 @@
         <v>19</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>250</v>
+        <v>19</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>184</v>
+        <v>252</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6300,10 +6282,10 @@
         <v>19</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="K44" t="s" s="2">
         <v>131</v>
@@ -6315,9 +6297,11 @@
         <v>254</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>19</v>
       </c>
@@ -6383,51 +6367,47 @@
         <v>19</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>251</v>
+        <v>129</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>257</v>
+        <v>19</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>131</v>
+        <v>263</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>258</v>
+        <v>307</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>19</v>
       </c>
@@ -6475,41 +6455,41 @@
         <v>19</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>260</v>
+        <v>306</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>129</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>19</v>
+        <v>310</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>84</v>
@@ -6521,10 +6501,10 @@
         <v>19</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>268</v>
+        <v>311</v>
       </c>
       <c r="L46" t="s" s="2">
         <v>312</v>
@@ -6557,13 +6537,11 @@
         <v>19</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>19</v>
+        <v>314</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>19</v>
@@ -6581,16 +6559,16 @@
         <v>19</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>19</v>
+        <v>315</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>96</v>
@@ -6604,18 +6582,18 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>315</v>
+        <v>19</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>84</v>
@@ -6627,16 +6605,16 @@
         <v>19</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6663,11 +6641,13 @@
         <v>19</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="Y47" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z47" t="s" s="2">
-        <v>319</v>
+        <v>19</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>19</v>
@@ -6685,16 +6665,16 @@
         <v>19</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>96</v>
@@ -6708,10 +6688,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6722,7 +6702,7 @@
         <v>75</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>19</v>
@@ -6734,13 +6714,13 @@
         <v>19</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>322</v>
+        <v>200</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6767,13 +6747,13 @@
         <v>19</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>19</v>
+        <v>322</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>19</v>
+        <v>323</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>19</v>
+        <v>324</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>19</v>
@@ -6791,16 +6771,16 @@
         <v>19</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>320</v>
+        <v>19</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>96</v>
@@ -6814,10 +6794,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6828,7 +6808,7 @@
         <v>75</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>19</v>
@@ -6840,13 +6820,13 @@
         <v>19</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>205</v>
+        <v>291</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6873,13 +6853,13 @@
         <v>19</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>327</v>
+        <v>19</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>328</v>
+        <v>19</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>329</v>
+        <v>19</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>19</v>
@@ -6897,13 +6877,13 @@
         <v>19</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>19</v>
@@ -6920,10 +6900,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6934,7 +6914,7 @@
         <v>75</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>19</v>
@@ -6946,13 +6926,13 @@
         <v>19</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>296</v>
+        <v>200</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6979,10 +6959,10 @@
         <v>19</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>19</v>
+        <v>203</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>19</v>
+        <v>331</v>
       </c>
       <c r="Z50" t="s" s="2">
         <v>19</v>
@@ -7003,13 +6983,13 @@
         <v>19</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>19</v>
@@ -7026,10 +7006,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7049,16 +7029,16 @@
         <v>19</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>205</v>
+        <v>236</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7085,10 +7065,10 @@
         <v>19</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>208</v>
+        <v>19</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>336</v>
+        <v>19</v>
       </c>
       <c r="Z51" t="s" s="2">
         <v>19</v>
@@ -7109,7 +7089,7 @@
         <v>19</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>75</v>
@@ -7121,7 +7101,7 @@
         <v>19</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>96</v>
+        <v>335</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>19</v>
@@ -7132,10 +7112,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7146,7 +7126,7 @@
         <v>75</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>19</v>
@@ -7155,16 +7135,16 @@
         <v>19</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>241</v>
+        <v>215</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>338</v>
+        <v>242</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>339</v>
+        <v>243</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7215,44 +7195,44 @@
         <v>19</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>337</v>
+        <v>244</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>19</v>
+        <v>245</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>340</v>
+        <v>19</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>19</v>
+        <v>246</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>19</v>
+        <v>179</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>19</v>
@@ -7264,15 +7244,17 @@
         <v>19</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>220</v>
+        <v>131</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>19</v>
@@ -7321,37 +7303,37 @@
         <v>19</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>250</v>
+        <v>19</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>184</v>
+        <v>252</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7364,10 +7346,10 @@
         <v>19</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="K54" t="s" s="2">
         <v>131</v>
@@ -7379,9 +7361,11 @@
         <v>254</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>19</v>
       </c>
@@ -7447,51 +7431,47 @@
         <v>19</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>251</v>
+        <v>129</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>257</v>
+        <v>19</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>131</v>
+        <v>263</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>258</v>
+        <v>340</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>341</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>19</v>
       </c>
@@ -7539,41 +7519,41 @@
         <v>19</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>260</v>
+        <v>339</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>129</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>19</v>
+        <v>310</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>84</v>
@@ -7585,16 +7565,16 @@
         <v>19</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>268</v>
+        <v>343</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7621,13 +7601,11 @@
         <v>19</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>19</v>
+        <v>346</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>19</v>
@@ -7645,16 +7623,16 @@
         <v>19</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>19</v>
+        <v>347</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>96</v>
@@ -7668,18 +7646,18 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>315</v>
+        <v>19</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>84</v>
@@ -7691,10 +7669,10 @@
         <v>19</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>348</v>
+        <v>317</v>
       </c>
       <c r="L57" t="s" s="2">
         <v>349</v>
@@ -7727,11 +7705,13 @@
         <v>19</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="Y57" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z57" t="s" s="2">
-        <v>351</v>
+        <v>19</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>19</v>
@@ -7749,16 +7729,16 @@
         <v>19</v>
       </c>
       <c r="AF57" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI57" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>96</v>
@@ -7772,10 +7752,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7786,7 +7766,7 @@
         <v>75</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>19</v>
@@ -7798,13 +7778,13 @@
         <v>19</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>322</v>
+        <v>200</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7831,10 +7811,10 @@
         <v>19</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>19</v>
+        <v>203</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>19</v>
+        <v>354</v>
       </c>
       <c r="Z58" t="s" s="2">
         <v>19</v>
@@ -7855,16 +7835,16 @@
         <v>19</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>352</v>
+        <v>19</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>96</v>
@@ -7878,10 +7858,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7904,13 +7884,13 @@
         <v>19</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>357</v>
+        <v>329</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7937,10 +7917,10 @@
         <v>19</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>359</v>
+        <v>331</v>
       </c>
       <c r="Z59" t="s" s="2">
         <v>19</v>
@@ -7961,7 +7941,7 @@
         <v>19</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>75</v>
@@ -7984,10 +7964,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8007,16 +7987,16 @@
         <v>19</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>205</v>
+        <v>358</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>334</v>
+        <v>359</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8043,10 +8023,10 @@
         <v>19</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>208</v>
+        <v>19</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>336</v>
+        <v>19</v>
       </c>
       <c r="Z60" t="s" s="2">
         <v>19</v>
@@ -8067,7 +8047,7 @@
         <v>19</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>75</v>
@@ -8090,10 +8070,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8113,16 +8093,16 @@
         <v>19</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8173,7 +8153,7 @@
         <v>19</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>75</v>
@@ -8196,10 +8176,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8210,7 +8190,7 @@
         <v>75</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>19</v>
@@ -8222,13 +8202,13 @@
         <v>19</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>241</v>
+        <v>215</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>367</v>
+        <v>242</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>368</v>
+        <v>243</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8279,44 +8259,44 @@
         <v>19</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>366</v>
+        <v>244</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>19</v>
+        <v>245</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>96</v>
+        <v>19</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>19</v>
+        <v>246</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>19</v>
+        <v>179</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>19</v>
@@ -8328,15 +8308,17 @@
         <v>19</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>220</v>
+        <v>131</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>19</v>
@@ -8385,37 +8367,37 @@
         <v>19</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>250</v>
+        <v>19</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>184</v>
+        <v>252</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -8428,10 +8410,10 @@
         <v>19</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="K64" t="s" s="2">
         <v>131</v>
@@ -8443,9 +8425,11 @@
         <v>254</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="O64" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>19</v>
       </c>
@@ -8511,51 +8495,47 @@
         <v>19</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>251</v>
+        <v>129</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>257</v>
+        <v>19</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>131</v>
+        <v>200</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>258</v>
+        <v>368</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>19</v>
       </c>
@@ -8579,13 +8559,13 @@
         <v>19</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>19</v>
+        <v>203</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>19</v>
+        <v>370</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>19</v>
+        <v>371</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>19</v>
@@ -8603,25 +8583,25 @@
         <v>19</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>260</v>
+        <v>367</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>129</v>
+        <v>19</v>
       </c>
     </row>
     <row r="66">
@@ -8637,7 +8617,7 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>84</v>
@@ -8652,13 +8632,13 @@
         <v>19</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>205</v>
+        <v>373</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8685,13 +8665,13 @@
         <v>19</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>208</v>
+        <v>19</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>375</v>
+        <v>19</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>376</v>
+        <v>19</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>19</v>
@@ -8712,7 +8692,7 @@
         <v>372</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>84</v>
@@ -8732,10 +8712,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8743,7 +8723,7 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>84</v>
@@ -8758,13 +8738,13 @@
         <v>19</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -8791,13 +8771,11 @@
         <v>19</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="Y67" s="2"/>
       <c r="Z67" t="s" s="2">
-        <v>19</v>
+        <v>379</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>19</v>
@@ -8815,10 +8793,10 @@
         <v>19</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>84</v>
@@ -8838,10 +8816,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8852,7 +8830,7 @@
         <v>75</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>19</v>
@@ -8864,13 +8842,13 @@
         <v>19</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>205</v>
+        <v>236</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -8897,11 +8875,13 @@
         <v>19</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="Y68" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z68" t="s" s="2">
-        <v>384</v>
+        <v>19</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>19</v>
@@ -8919,13 +8899,13 @@
         <v>19</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>19</v>
@@ -8942,10 +8922,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8956,7 +8936,7 @@
         <v>75</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>19</v>
@@ -8968,13 +8948,13 @@
         <v>19</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>241</v>
+        <v>215</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>386</v>
+        <v>242</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>387</v>
+        <v>243</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9025,44 +9005,44 @@
         <v>19</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>385</v>
+        <v>244</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>19</v>
+        <v>245</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>96</v>
+        <v>19</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>19</v>
+        <v>246</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>19</v>
+        <v>179</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>19</v>
@@ -9074,15 +9054,17 @@
         <v>19</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>220</v>
+        <v>131</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>19</v>
@@ -9131,37 +9113,37 @@
         <v>19</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>250</v>
+        <v>19</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>184</v>
+        <v>252</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -9174,10 +9156,10 @@
         <v>19</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="K71" t="s" s="2">
         <v>131</v>
@@ -9189,9 +9171,11 @@
         <v>254</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="O71" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>19</v>
       </c>
@@ -9257,51 +9241,47 @@
         <v>19</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>251</v>
+        <v>129</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>257</v>
+        <v>19</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>131</v>
+        <v>200</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>258</v>
+        <v>387</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>19</v>
       </c>
@@ -9325,13 +9305,13 @@
         <v>19</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>19</v>
+        <v>389</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>19</v>
+        <v>390</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>19</v>
+        <v>391</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>19</v>
@@ -9349,33 +9329,33 @@
         <v>19</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>260</v>
+        <v>386</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>129</v>
+        <v>19</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9398,13 +9378,13 @@
         <v>19</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9431,14 +9411,14 @@
         <v>19</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="Y73" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="Z73" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="Z73" t="s" s="2">
-        <v>396</v>
-      </c>
       <c r="AA73" t="s" s="2">
         <v>19</v>
       </c>
@@ -9455,7 +9435,7 @@
         <v>19</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>75</v>
@@ -9478,10 +9458,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9504,13 +9484,13 @@
         <v>19</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>205</v>
+        <v>291</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -9537,13 +9517,13 @@
         <v>19</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>394</v>
+        <v>19</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>395</v>
+        <v>19</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>400</v>
+        <v>19</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>19</v>
@@ -9561,7 +9541,7 @@
         <v>19</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>75</v>
@@ -9584,10 +9564,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9595,7 +9575,7 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>84</v>
@@ -9610,13 +9590,13 @@
         <v>19</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>296</v>
+        <v>400</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -9667,10 +9647,10 @@
         <v>19</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AH75" t="s" s="2">
         <v>84</v>
@@ -9690,10 +9670,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9701,7 +9681,7 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>84</v>
@@ -9716,15 +9696,17 @@
         <v>19</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="L76" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="M76" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>19</v>
@@ -9773,10 +9755,10 @@
         <v>19</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AH76" t="s" s="2">
         <v>84</v>
@@ -9791,114 +9773,6 @@
         <v>19</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="C77" s="2"/>
-      <c r="D77" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="E77" s="2"/>
-      <c r="F77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="K77" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="O77" s="2"/>
-      <c r="P77" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q77" s="2"/>
-      <c r="R77" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S77" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T77" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U77" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="AG77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI77" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AJ77" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL77" t="s" s="2">
         <v>19</v>
       </c>
     </row>
